--- a/experiment_results/wu_calibration/rtt_bursts_rps5_att4_WU200000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps5_att4_WU200000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,22 +538,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>21.10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>24691</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.7</t>
+          <t>00:029.9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36204</t>
+          <t>55623</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,17 +647,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.2</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44679</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,22 +704,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.9</t>
+          <t>00:050.3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>101177</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:060.0</t>
+          <t>00:059.8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80908</t>
+          <t>136648</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.7</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100187</t>
+          <t>168255</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:020.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>116540</t>
+          <t>191388</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.3</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>126078</t>
+          <t>214054</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,12 +989,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:040.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>142541</t>
+          <t>232749</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>156238</t>
+          <t>258277</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.9</t>
+          <t>02:000.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>175700</t>
+          <t>288185</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>212908</t>
+          <t>314150</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:019.9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>239541</t>
+          <t>338005</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:029.9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>246779</t>
+          <t>358780</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.1</t>
+          <t>02:039.2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>243718</t>
+          <t>364059</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.9</t>
+          <t>02:050.2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>234442</t>
+          <t>356601</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.9</t>
+          <t>02:055.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>229758</t>
+          <t>352855</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
